--- a/academias/Física - Estadisticos 20212.xlsx
+++ b/academias/Física - Estadisticos 20212.xlsx
@@ -540,22 +540,25 @@
         <v>38</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F2">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="G2" s="1">
-        <v>0</v>
+        <v>39.47</v>
       </c>
       <c r="H2" s="1">
-        <v>100</v>
+        <v>60.53</v>
+      </c>
+      <c r="I2" s="2">
+        <v>8.6</v>
       </c>
       <c r="J2">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="K2" s="1">
-        <v>100</v>
+        <v>60.53</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -572,22 +575,25 @@
         <v>24</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F3">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="G3" s="1">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H3" s="1">
-        <v>100</v>
+        <v>75</v>
+      </c>
+      <c r="I3" s="2">
+        <v>6.7</v>
       </c>
       <c r="J3">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="K3" s="1">
-        <v>100</v>
+        <v>75</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -604,22 +610,25 @@
         <v>31</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F4">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>19.35</v>
       </c>
       <c r="H4" s="1">
-        <v>100</v>
+        <v>80.65000000000001</v>
+      </c>
+      <c r="I4" s="2">
+        <v>7.2</v>
       </c>
       <c r="J4">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="K4" s="1">
-        <v>100</v>
+        <v>80.65000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -636,22 +645,25 @@
         <v>19</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F5">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
+        <v>21.05</v>
       </c>
       <c r="H5" s="1">
-        <v>100</v>
+        <v>78.95</v>
+      </c>
+      <c r="I5" s="2">
+        <v>7.3</v>
       </c>
       <c r="J5">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="K5" s="1">
-        <v>100</v>
+        <v>78.95</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -668,22 +680,25 @@
         <v>32</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F6">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>53.13</v>
       </c>
       <c r="H6" s="1">
-        <v>100</v>
+        <v>46.88</v>
+      </c>
+      <c r="I6" s="2">
+        <v>7.9</v>
       </c>
       <c r="J6">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="K6" s="1">
-        <v>100</v>
+        <v>46.88</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -700,22 +715,25 @@
         <v>32</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F7">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="G7" s="1">
-        <v>0</v>
+        <v>56.25</v>
       </c>
       <c r="H7" s="1">
-        <v>100</v>
+        <v>43.75</v>
+      </c>
+      <c r="I7" s="2">
+        <v>6.4</v>
       </c>
       <c r="J7">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="K7" s="1">
-        <v>100</v>
+        <v>43.75</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -892,22 +910,25 @@
         <v>32</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F13">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="G13" s="1">
-        <v>0</v>
+        <v>96.88</v>
       </c>
       <c r="H13" s="1">
-        <v>100</v>
+        <v>3.13</v>
+      </c>
+      <c r="I13" s="2">
+        <v>6.3</v>
       </c>
       <c r="J13">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -924,22 +945,25 @@
         <v>24</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F14">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="G14" s="1">
-        <v>0</v>
+        <v>83.33</v>
       </c>
       <c r="H14" s="1">
-        <v>100</v>
+        <v>16.67</v>
+      </c>
+      <c r="I14" s="2">
+        <v>6.3</v>
       </c>
       <c r="J14">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K14" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -956,22 +980,25 @@
         <v>32</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F15">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="G15" s="1">
-        <v>0</v>
+        <v>93.75</v>
       </c>
       <c r="H15" s="1">
-        <v>100</v>
+        <v>6.25</v>
+      </c>
+      <c r="I15" s="2">
+        <v>6.4</v>
       </c>
       <c r="J15">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K15" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -1058,22 +1085,25 @@
         <v>19</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F18">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G18" s="1">
-        <v>0</v>
+        <v>21.05</v>
       </c>
       <c r="H18" s="1">
-        <v>100</v>
+        <v>78.95</v>
+      </c>
+      <c r="I18" s="2">
+        <v>6.8</v>
       </c>
       <c r="J18">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="K18" s="1">
-        <v>100</v>
+        <v>78.95</v>
       </c>
     </row>
   </sheetData>
@@ -1738,22 +1768,25 @@
         <v>38</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F2">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="G2" s="1">
-        <v>0</v>
+        <v>39.47</v>
       </c>
       <c r="H2" s="1">
-        <v>100</v>
+        <v>60.53</v>
+      </c>
+      <c r="I2" s="2">
+        <v>8.6</v>
       </c>
       <c r="J2">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="K2" s="1">
-        <v>100</v>
+        <v>60.53</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1770,22 +1803,25 @@
         <v>24</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F3">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="G3" s="1">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H3" s="1">
-        <v>100</v>
+        <v>75</v>
+      </c>
+      <c r="I3" s="2">
+        <v>6.7</v>
       </c>
       <c r="J3">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="K3" s="1">
-        <v>100</v>
+        <v>75</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1802,22 +1838,25 @@
         <v>31</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F4">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>19.35</v>
       </c>
       <c r="H4" s="1">
-        <v>100</v>
+        <v>80.65000000000001</v>
+      </c>
+      <c r="I4" s="2">
+        <v>7.2</v>
       </c>
       <c r="J4">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="K4" s="1">
-        <v>100</v>
+        <v>80.65000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1834,22 +1873,25 @@
         <v>19</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F5">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
+        <v>21.05</v>
       </c>
       <c r="H5" s="1">
-        <v>100</v>
+        <v>78.95</v>
+      </c>
+      <c r="I5" s="2">
+        <v>7.3</v>
       </c>
       <c r="J5">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="K5" s="1">
-        <v>100</v>
+        <v>78.95</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1866,22 +1908,25 @@
         <v>32</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F6">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>53.13</v>
       </c>
       <c r="H6" s="1">
-        <v>100</v>
+        <v>46.88</v>
+      </c>
+      <c r="I6" s="2">
+        <v>7.9</v>
       </c>
       <c r="J6">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="K6" s="1">
-        <v>100</v>
+        <v>46.88</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1898,22 +1943,25 @@
         <v>32</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F7">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="G7" s="1">
-        <v>0</v>
+        <v>56.25</v>
       </c>
       <c r="H7" s="1">
-        <v>100</v>
+        <v>43.75</v>
+      </c>
+      <c r="I7" s="2">
+        <v>6.4</v>
       </c>
       <c r="J7">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="K7" s="1">
-        <v>100</v>
+        <v>43.75</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -2090,22 +2138,25 @@
         <v>32</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F13">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="G13" s="1">
-        <v>0</v>
+        <v>96.88</v>
       </c>
       <c r="H13" s="1">
-        <v>100</v>
+        <v>3.13</v>
+      </c>
+      <c r="I13" s="2">
+        <v>6.3</v>
       </c>
       <c r="J13">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -2122,22 +2173,25 @@
         <v>24</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F14">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="G14" s="1">
-        <v>0</v>
+        <v>83.33</v>
       </c>
       <c r="H14" s="1">
-        <v>100</v>
+        <v>16.67</v>
+      </c>
+      <c r="I14" s="2">
+        <v>6.3</v>
       </c>
       <c r="J14">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K14" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -2154,22 +2208,25 @@
         <v>32</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F15">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="G15" s="1">
-        <v>0</v>
+        <v>93.75</v>
       </c>
       <c r="H15" s="1">
-        <v>100</v>
+        <v>6.25</v>
+      </c>
+      <c r="I15" s="2">
+        <v>6.4</v>
       </c>
       <c r="J15">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K15" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -2256,22 +2313,25 @@
         <v>19</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F18">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G18" s="1">
-        <v>0</v>
+        <v>21.05</v>
       </c>
       <c r="H18" s="1">
-        <v>100</v>
+        <v>78.95</v>
+      </c>
+      <c r="I18" s="2">
+        <v>6.8</v>
       </c>
       <c r="J18">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="K18" s="1">
-        <v>100</v>
+        <v>78.95</v>
       </c>
     </row>
   </sheetData>

--- a/academias/Física - Estadisticos 20212.xlsx
+++ b/academias/Física - Estadisticos 20212.xlsx
@@ -540,25 +540,25 @@
         <v>38</v>
       </c>
       <c r="E2">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F2">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="G2" s="1">
-        <v>39.47</v>
+        <v>78.95</v>
       </c>
       <c r="H2" s="1">
-        <v>60.53</v>
+        <v>21.05</v>
       </c>
       <c r="I2" s="2">
-        <v>8.6</v>
+        <v>7.3</v>
       </c>
       <c r="J2">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="K2" s="1">
-        <v>60.53</v>
+        <v>21.05</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -575,25 +575,25 @@
         <v>24</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="F3">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="G3" s="1">
-        <v>25</v>
+        <v>87.5</v>
       </c>
       <c r="H3" s="1">
-        <v>75</v>
+        <v>12.5</v>
       </c>
       <c r="I3" s="2">
-        <v>6.7</v>
+        <v>6.2</v>
       </c>
       <c r="J3">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="K3" s="1">
-        <v>75</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -610,25 +610,25 @@
         <v>31</v>
       </c>
       <c r="E4">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="F4">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="G4" s="1">
-        <v>19.35</v>
+        <v>70.97</v>
       </c>
       <c r="H4" s="1">
-        <v>80.65000000000001</v>
+        <v>29.03</v>
       </c>
       <c r="I4" s="2">
-        <v>7.2</v>
+        <v>6.3</v>
       </c>
       <c r="J4">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="K4" s="1">
-        <v>80.65000000000001</v>
+        <v>29.03</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -645,25 +645,25 @@
         <v>19</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F5">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="G5" s="1">
-        <v>21.05</v>
+        <v>63.16</v>
       </c>
       <c r="H5" s="1">
-        <v>78.95</v>
+        <v>36.84</v>
       </c>
       <c r="I5" s="2">
-        <v>7.3</v>
+        <v>6.5</v>
       </c>
       <c r="J5">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="K5" s="1">
-        <v>78.95</v>
+        <v>36.84</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -680,25 +680,25 @@
         <v>32</v>
       </c>
       <c r="E6">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F6">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="G6" s="1">
-        <v>53.13</v>
+        <v>78.13</v>
       </c>
       <c r="H6" s="1">
-        <v>46.88</v>
+        <v>21.88</v>
       </c>
       <c r="I6" s="2">
-        <v>7.9</v>
+        <v>7.3</v>
       </c>
       <c r="J6">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="K6" s="1">
-        <v>46.88</v>
+        <v>21.88</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -715,25 +715,25 @@
         <v>32</v>
       </c>
       <c r="E7">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F7">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="G7" s="1">
-        <v>56.25</v>
+        <v>71.88</v>
       </c>
       <c r="H7" s="1">
-        <v>43.75</v>
+        <v>28.13</v>
       </c>
       <c r="I7" s="2">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="J7">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="K7" s="1">
-        <v>43.75</v>
+        <v>28.13</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -750,22 +750,25 @@
         <v>37</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F8">
-        <v>37</v>
+        <v>7</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>81.08</v>
       </c>
       <c r="H8" s="1">
-        <v>100</v>
+        <v>18.92</v>
+      </c>
+      <c r="I8" s="2">
+        <v>8.300000000000001</v>
       </c>
       <c r="J8">
-        <v>37</v>
+        <v>7</v>
       </c>
       <c r="K8" s="1">
-        <v>100</v>
+        <v>18.92</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -782,22 +785,25 @@
         <v>36</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F9">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="G9" s="1">
-        <v>0</v>
+        <v>69.44</v>
       </c>
       <c r="H9" s="1">
-        <v>100</v>
+        <v>30.56</v>
+      </c>
+      <c r="I9" s="2">
+        <v>7.8</v>
       </c>
       <c r="J9">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="K9" s="1">
-        <v>100</v>
+        <v>30.56</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -814,22 +820,25 @@
         <v>33</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F10">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="G10" s="1">
-        <v>0</v>
+        <v>69.7</v>
       </c>
       <c r="H10" s="1">
-        <v>100</v>
+        <v>30.3</v>
+      </c>
+      <c r="I10" s="2">
+        <v>7.6</v>
       </c>
       <c r="J10">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="K10" s="1">
-        <v>100</v>
+        <v>30.3</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -846,22 +855,25 @@
         <v>31</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F11">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="G11" s="1">
-        <v>0</v>
+        <v>9.68</v>
       </c>
       <c r="H11" s="1">
-        <v>100</v>
+        <v>90.31999999999999</v>
+      </c>
+      <c r="I11" s="2">
+        <v>7.3</v>
       </c>
       <c r="J11">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="K11" s="1">
-        <v>100</v>
+        <v>90.31999999999999</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -878,22 +890,25 @@
         <v>34</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F12">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="G12" s="1">
-        <v>0</v>
+        <v>67.65000000000001</v>
       </c>
       <c r="H12" s="1">
-        <v>100</v>
+        <v>32.35</v>
+      </c>
+      <c r="I12" s="2">
+        <v>7.7</v>
       </c>
       <c r="J12">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="K12" s="1">
-        <v>100</v>
+        <v>32.35</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -1768,25 +1783,25 @@
         <v>38</v>
       </c>
       <c r="E2">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F2">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="G2" s="1">
-        <v>39.47</v>
+        <v>78.95</v>
       </c>
       <c r="H2" s="1">
-        <v>60.53</v>
+        <v>21.05</v>
       </c>
       <c r="I2" s="2">
-        <v>8.6</v>
+        <v>7.3</v>
       </c>
       <c r="J2">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="K2" s="1">
-        <v>60.53</v>
+        <v>21.05</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1803,25 +1818,25 @@
         <v>24</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="F3">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="G3" s="1">
-        <v>25</v>
+        <v>87.5</v>
       </c>
       <c r="H3" s="1">
-        <v>75</v>
+        <v>12.5</v>
       </c>
       <c r="I3" s="2">
-        <v>6.7</v>
+        <v>6.2</v>
       </c>
       <c r="J3">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="K3" s="1">
-        <v>75</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1838,25 +1853,25 @@
         <v>31</v>
       </c>
       <c r="E4">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="F4">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="G4" s="1">
-        <v>19.35</v>
+        <v>70.97</v>
       </c>
       <c r="H4" s="1">
-        <v>80.65000000000001</v>
+        <v>29.03</v>
       </c>
       <c r="I4" s="2">
-        <v>7.2</v>
+        <v>6.3</v>
       </c>
       <c r="J4">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="K4" s="1">
-        <v>80.65000000000001</v>
+        <v>29.03</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1873,25 +1888,25 @@
         <v>19</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F5">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="G5" s="1">
-        <v>21.05</v>
+        <v>63.16</v>
       </c>
       <c r="H5" s="1">
-        <v>78.95</v>
+        <v>36.84</v>
       </c>
       <c r="I5" s="2">
-        <v>7.3</v>
+        <v>6.5</v>
       </c>
       <c r="J5">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="K5" s="1">
-        <v>78.95</v>
+        <v>36.84</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1908,25 +1923,25 @@
         <v>32</v>
       </c>
       <c r="E6">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F6">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="G6" s="1">
-        <v>53.13</v>
+        <v>78.13</v>
       </c>
       <c r="H6" s="1">
-        <v>46.88</v>
+        <v>21.88</v>
       </c>
       <c r="I6" s="2">
-        <v>7.9</v>
+        <v>7.3</v>
       </c>
       <c r="J6">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="K6" s="1">
-        <v>46.88</v>
+        <v>21.88</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1943,25 +1958,25 @@
         <v>32</v>
       </c>
       <c r="E7">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F7">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="G7" s="1">
-        <v>56.25</v>
+        <v>71.88</v>
       </c>
       <c r="H7" s="1">
-        <v>43.75</v>
+        <v>28.13</v>
       </c>
       <c r="I7" s="2">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="J7">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="K7" s="1">
-        <v>43.75</v>
+        <v>28.13</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1978,22 +1993,25 @@
         <v>37</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F8">
-        <v>37</v>
+        <v>7</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>81.08</v>
       </c>
       <c r="H8" s="1">
-        <v>100</v>
+        <v>18.92</v>
+      </c>
+      <c r="I8" s="2">
+        <v>8.300000000000001</v>
       </c>
       <c r="J8">
-        <v>37</v>
+        <v>7</v>
       </c>
       <c r="K8" s="1">
-        <v>100</v>
+        <v>18.92</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -2010,22 +2028,25 @@
         <v>36</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F9">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="G9" s="1">
-        <v>0</v>
+        <v>69.44</v>
       </c>
       <c r="H9" s="1">
-        <v>100</v>
+        <v>30.56</v>
+      </c>
+      <c r="I9" s="2">
+        <v>7.8</v>
       </c>
       <c r="J9">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="K9" s="1">
-        <v>100</v>
+        <v>30.56</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -2042,22 +2063,25 @@
         <v>33</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F10">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="G10" s="1">
-        <v>0</v>
+        <v>69.7</v>
       </c>
       <c r="H10" s="1">
-        <v>100</v>
+        <v>30.3</v>
+      </c>
+      <c r="I10" s="2">
+        <v>7.6</v>
       </c>
       <c r="J10">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="K10" s="1">
-        <v>100</v>
+        <v>30.3</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -2074,22 +2098,25 @@
         <v>31</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F11">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="G11" s="1">
-        <v>0</v>
+        <v>9.68</v>
       </c>
       <c r="H11" s="1">
-        <v>100</v>
+        <v>90.31999999999999</v>
+      </c>
+      <c r="I11" s="2">
+        <v>7.3</v>
       </c>
       <c r="J11">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="K11" s="1">
-        <v>100</v>
+        <v>90.31999999999999</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -2106,22 +2133,25 @@
         <v>34</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F12">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="G12" s="1">
-        <v>0</v>
+        <v>67.65000000000001</v>
       </c>
       <c r="H12" s="1">
-        <v>100</v>
+        <v>32.35</v>
+      </c>
+      <c r="I12" s="2">
+        <v>7.7</v>
       </c>
       <c r="J12">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="K12" s="1">
-        <v>100</v>
+        <v>32.35</v>
       </c>
     </row>
     <row r="13" spans="1:11">

--- a/academias/Física - Estadisticos 20212.xlsx
+++ b/academias/Física - Estadisticos 20212.xlsx
@@ -540,25 +540,25 @@
         <v>38</v>
       </c>
       <c r="E2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G2" s="1">
-        <v>78.95</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="H2" s="1">
-        <v>21.05</v>
+        <v>15.79</v>
       </c>
       <c r="I2" s="2">
-        <v>7.3</v>
+        <v>6.9</v>
       </c>
       <c r="J2">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>21.05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -575,25 +575,25 @@
         <v>24</v>
       </c>
       <c r="E3">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G3" s="1">
-        <v>87.5</v>
+        <v>91.67</v>
       </c>
       <c r="H3" s="1">
-        <v>12.5</v>
+        <v>8.33</v>
       </c>
       <c r="I3" s="2">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="J3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>12.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -610,25 +610,25 @@
         <v>31</v>
       </c>
       <c r="E4">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F4">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G4" s="1">
-        <v>70.97</v>
+        <v>83.87</v>
       </c>
       <c r="H4" s="1">
-        <v>29.03</v>
+        <v>16.13</v>
       </c>
       <c r="I4" s="2">
-        <v>6.3</v>
+        <v>6.1</v>
       </c>
       <c r="J4">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>29.03</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -645,25 +645,25 @@
         <v>19</v>
       </c>
       <c r="E5">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F5">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G5" s="1">
-        <v>63.16</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="H5" s="1">
-        <v>36.84</v>
+        <v>26.32</v>
       </c>
       <c r="I5" s="2">
-        <v>6.5</v>
+        <v>6.1</v>
       </c>
       <c r="J5">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>36.84</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -680,25 +680,25 @@
         <v>32</v>
       </c>
       <c r="E6">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G6" s="1">
-        <v>78.13</v>
+        <v>81.25</v>
       </c>
       <c r="H6" s="1">
-        <v>21.88</v>
+        <v>18.75</v>
       </c>
       <c r="I6" s="2">
-        <v>7.3</v>
+        <v>6.8</v>
       </c>
       <c r="J6">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>21.88</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -715,25 +715,25 @@
         <v>32</v>
       </c>
       <c r="E7">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="F7">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G7" s="1">
-        <v>71.88</v>
+        <v>93.75</v>
       </c>
       <c r="H7" s="1">
-        <v>28.13</v>
+        <v>6.25</v>
       </c>
       <c r="I7" s="2">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="J7">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>28.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -747,28 +747,28 @@
         <v>33</v>
       </c>
       <c r="D8">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E8">
         <v>30</v>
       </c>
       <c r="F8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G8" s="1">
-        <v>81.08</v>
+        <v>83.33</v>
       </c>
       <c r="H8" s="1">
-        <v>18.92</v>
+        <v>16.67</v>
       </c>
       <c r="I8" s="2">
         <v>8.300000000000001</v>
       </c>
       <c r="J8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K8" s="1">
-        <v>18.92</v>
+        <v>16.67</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1027,28 +1027,28 @@
         <v>33</v>
       </c>
       <c r="D16">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E16">
+        <v>25</v>
+      </c>
+      <c r="F16">
         <v>4</v>
       </c>
-      <c r="F16">
-        <v>24</v>
-      </c>
       <c r="G16" s="1">
-        <v>14.29</v>
+        <v>86.20999999999999</v>
       </c>
       <c r="H16" s="1">
-        <v>85.70999999999999</v>
+        <v>13.79</v>
       </c>
       <c r="I16" s="2">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="J16">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K16" s="1">
-        <v>85.70999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -1065,25 +1065,25 @@
         <v>20</v>
       </c>
       <c r="E17">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F17">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="G17" s="1">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="H17" s="1">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="I17" s="2">
-        <v>7.3</v>
+        <v>5.8</v>
       </c>
       <c r="J17">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="K17" s="1">
-        <v>85</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -1100,25 +1100,25 @@
         <v>19</v>
       </c>
       <c r="E18">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F18">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="G18" s="1">
-        <v>21.05</v>
+        <v>63.16</v>
       </c>
       <c r="H18" s="1">
-        <v>78.95</v>
+        <v>36.84</v>
       </c>
       <c r="I18" s="2">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="J18">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="K18" s="1">
-        <v>78.95</v>
+        <v>10.53</v>
       </c>
     </row>
   </sheetData>
@@ -1187,22 +1187,25 @@
         <v>38</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F2">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="G2" s="1">
-        <v>0</v>
+        <v>52.63</v>
       </c>
       <c r="H2" s="1">
-        <v>100</v>
+        <v>47.37</v>
+      </c>
+      <c r="I2" s="2">
+        <v>6.3</v>
       </c>
       <c r="J2">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1219,22 +1222,25 @@
         <v>24</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F3">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="G3" s="1">
-        <v>0</v>
+        <v>29.17</v>
       </c>
       <c r="H3" s="1">
-        <v>100</v>
+        <v>70.83</v>
+      </c>
+      <c r="I3" s="2">
+        <v>6.1</v>
       </c>
       <c r="J3">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="K3" s="1">
-        <v>100</v>
+        <v>16.67</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1251,22 +1257,25 @@
         <v>31</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F4">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>51.61</v>
       </c>
       <c r="H4" s="1">
-        <v>100</v>
+        <v>48.39</v>
+      </c>
+      <c r="I4" s="2">
+        <v>6.3</v>
       </c>
       <c r="J4">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1283,22 +1292,25 @@
         <v>19</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F5">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
+        <v>52.63</v>
       </c>
       <c r="H5" s="1">
-        <v>100</v>
+        <v>47.37</v>
+      </c>
+      <c r="I5" s="2">
+        <v>6.4</v>
       </c>
       <c r="J5">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1315,22 +1327,25 @@
         <v>32</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F6">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>53.13</v>
       </c>
       <c r="H6" s="1">
-        <v>100</v>
+        <v>46.88</v>
+      </c>
+      <c r="I6" s="2">
+        <v>6.6</v>
       </c>
       <c r="J6">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="K6" s="1">
-        <v>100</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1347,22 +1362,25 @@
         <v>32</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F7">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="G7" s="1">
-        <v>0</v>
+        <v>43.75</v>
       </c>
       <c r="H7" s="1">
-        <v>100</v>
+        <v>56.25</v>
+      </c>
+      <c r="I7" s="2">
+        <v>6</v>
       </c>
       <c r="J7">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="K7" s="1">
-        <v>100</v>
+        <v>9.380000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1376,13 +1394,13 @@
         <v>33</v>
       </c>
       <c r="D8">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E8">
         <v>0</v>
       </c>
       <c r="F8">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G8" s="1">
         <v>0</v>
@@ -1391,7 +1409,7 @@
         <v>100</v>
       </c>
       <c r="J8">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K8" s="1">
         <v>100</v>
@@ -1632,25 +1650,28 @@
         <v>33</v>
       </c>
       <c r="D16">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F16">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="G16" s="1">
-        <v>0</v>
+        <v>79.31</v>
       </c>
       <c r="H16" s="1">
-        <v>100</v>
+        <v>20.69</v>
+      </c>
+      <c r="I16" s="2">
+        <v>7.4</v>
       </c>
       <c r="J16">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="K16" s="1">
-        <v>100</v>
+        <v>10.34</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -1667,22 +1688,25 @@
         <v>20</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F17">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="G17" s="1">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H17" s="1">
-        <v>100</v>
+        <v>65</v>
+      </c>
+      <c r="I17" s="2">
+        <v>5.7</v>
       </c>
       <c r="J17">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="K17" s="1">
-        <v>100</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -1699,22 +1723,25 @@
         <v>19</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F18">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="G18" s="1">
-        <v>0</v>
+        <v>57.89</v>
       </c>
       <c r="H18" s="1">
-        <v>100</v>
+        <v>42.11</v>
+      </c>
+      <c r="I18" s="2">
+        <v>7</v>
       </c>
       <c r="J18">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="K18" s="1">
-        <v>100</v>
+        <v>10.53</v>
       </c>
     </row>
   </sheetData>
@@ -1783,25 +1810,25 @@
         <v>38</v>
       </c>
       <c r="E2">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F2">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="G2" s="1">
-        <v>78.95</v>
+        <v>52.63</v>
       </c>
       <c r="H2" s="1">
-        <v>21.05</v>
+        <v>47.37</v>
       </c>
       <c r="I2" s="2">
-        <v>7.3</v>
+        <v>6.6</v>
       </c>
       <c r="J2">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>21.05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1818,25 +1845,25 @@
         <v>24</v>
       </c>
       <c r="E3">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="G3" s="1">
-        <v>87.5</v>
+        <v>41.67</v>
       </c>
       <c r="H3" s="1">
-        <v>12.5</v>
+        <v>58.33</v>
       </c>
       <c r="I3" s="2">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="J3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>12.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1853,25 +1880,25 @@
         <v>31</v>
       </c>
       <c r="E4">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="F4">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="G4" s="1">
-        <v>70.97</v>
+        <v>51.61</v>
       </c>
       <c r="H4" s="1">
-        <v>29.03</v>
+        <v>48.39</v>
       </c>
       <c r="I4" s="2">
-        <v>6.3</v>
+        <v>6.1</v>
       </c>
       <c r="J4">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>29.03</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1888,25 +1915,25 @@
         <v>19</v>
       </c>
       <c r="E5">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F5">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G5" s="1">
-        <v>63.16</v>
+        <v>52.63</v>
       </c>
       <c r="H5" s="1">
-        <v>36.84</v>
+        <v>47.37</v>
       </c>
       <c r="I5" s="2">
-        <v>6.5</v>
+        <v>6.2</v>
       </c>
       <c r="J5">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>36.84</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1923,25 +1950,25 @@
         <v>32</v>
       </c>
       <c r="E6">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="F6">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="G6" s="1">
-        <v>78.13</v>
+        <v>59.38</v>
       </c>
       <c r="H6" s="1">
-        <v>21.88</v>
+        <v>40.63</v>
       </c>
       <c r="I6" s="2">
-        <v>7.3</v>
+        <v>6.7</v>
       </c>
       <c r="J6">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>21.88</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1958,25 +1985,25 @@
         <v>32</v>
       </c>
       <c r="E7">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F7">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="G7" s="1">
-        <v>71.88</v>
+        <v>53.13</v>
       </c>
       <c r="H7" s="1">
-        <v>28.13</v>
+        <v>46.88</v>
       </c>
       <c r="I7" s="2">
-        <v>6.3</v>
+        <v>6</v>
       </c>
       <c r="J7">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>28.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1990,28 +2017,28 @@
         <v>33</v>
       </c>
       <c r="D8">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E8">
         <v>30</v>
       </c>
       <c r="F8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G8" s="1">
-        <v>81.08</v>
+        <v>83.33</v>
       </c>
       <c r="H8" s="1">
-        <v>18.92</v>
+        <v>16.67</v>
       </c>
       <c r="I8" s="2">
         <v>8.300000000000001</v>
       </c>
       <c r="J8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K8" s="1">
-        <v>18.92</v>
+        <v>16.67</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -2270,28 +2297,28 @@
         <v>33</v>
       </c>
       <c r="D16">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E16">
+        <v>25</v>
+      </c>
+      <c r="F16">
         <v>4</v>
       </c>
-      <c r="F16">
-        <v>24</v>
-      </c>
       <c r="G16" s="1">
-        <v>14.29</v>
+        <v>86.20999999999999</v>
       </c>
       <c r="H16" s="1">
-        <v>85.70999999999999</v>
+        <v>13.79</v>
       </c>
       <c r="I16" s="2">
         <v>6.8</v>
       </c>
       <c r="J16">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K16" s="1">
-        <v>85.70999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -2308,25 +2335,25 @@
         <v>20</v>
       </c>
       <c r="E17">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F17">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="G17" s="1">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="H17" s="1">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="I17" s="2">
-        <v>7.3</v>
+        <v>5.8</v>
       </c>
       <c r="J17">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="K17" s="1">
-        <v>85</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -2343,25 +2370,25 @@
         <v>19</v>
       </c>
       <c r="E18">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F18">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="G18" s="1">
-        <v>21.05</v>
+        <v>57.89</v>
       </c>
       <c r="H18" s="1">
-        <v>78.95</v>
+        <v>42.11</v>
       </c>
       <c r="I18" s="2">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="J18">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="K18" s="1">
-        <v>78.95</v>
+        <v>10.53</v>
       </c>
     </row>
   </sheetData>

--- a/academias/Física - Estadisticos 20212.xlsx
+++ b/academias/Física - Estadisticos 20212.xlsx
@@ -750,25 +750,25 @@
         <v>36</v>
       </c>
       <c r="E8">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F8">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G8" s="1">
-        <v>83.33</v>
+        <v>94.44</v>
       </c>
       <c r="H8" s="1">
-        <v>16.67</v>
+        <v>5.56</v>
       </c>
       <c r="I8" s="2">
-        <v>8.300000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="J8">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>16.67</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -785,25 +785,25 @@
         <v>36</v>
       </c>
       <c r="E9">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F9">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="G9" s="1">
-        <v>69.44</v>
+        <v>83.33</v>
       </c>
       <c r="H9" s="1">
-        <v>30.56</v>
+        <v>16.67</v>
       </c>
       <c r="I9" s="2">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="J9">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>30.56</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -820,25 +820,25 @@
         <v>33</v>
       </c>
       <c r="E10">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F10">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G10" s="1">
-        <v>69.7</v>
+        <v>78.79000000000001</v>
       </c>
       <c r="H10" s="1">
-        <v>30.3</v>
+        <v>21.21</v>
       </c>
       <c r="I10" s="2">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="J10">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>30.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -855,25 +855,25 @@
         <v>31</v>
       </c>
       <c r="E11">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="F11">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="G11" s="1">
-        <v>9.68</v>
+        <v>35.48</v>
       </c>
       <c r="H11" s="1">
-        <v>90.31999999999999</v>
+        <v>64.52</v>
       </c>
       <c r="I11" s="2">
-        <v>7.3</v>
+        <v>5</v>
       </c>
       <c r="J11">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>90.31999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -890,25 +890,25 @@
         <v>34</v>
       </c>
       <c r="E12">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F12">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G12" s="1">
-        <v>67.65000000000001</v>
+        <v>76.47</v>
       </c>
       <c r="H12" s="1">
-        <v>32.35</v>
+        <v>23.53</v>
       </c>
       <c r="I12" s="2">
-        <v>7.7</v>
+        <v>6.8</v>
       </c>
       <c r="J12">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>32.35</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -1397,22 +1397,25 @@
         <v>36</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F8">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>91.67</v>
       </c>
       <c r="H8" s="1">
-        <v>100</v>
+        <v>8.33</v>
+      </c>
+      <c r="I8" s="2">
+        <v>7.7</v>
       </c>
       <c r="J8">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1429,22 +1432,25 @@
         <v>36</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F9">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="G9" s="1">
-        <v>0</v>
+        <v>77.78</v>
       </c>
       <c r="H9" s="1">
-        <v>100</v>
+        <v>22.22</v>
+      </c>
+      <c r="I9" s="2">
+        <v>7</v>
       </c>
       <c r="J9">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1461,22 +1467,25 @@
         <v>33</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F10">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="G10" s="1">
-        <v>0</v>
+        <v>72.73</v>
       </c>
       <c r="H10" s="1">
-        <v>100</v>
+        <v>27.27</v>
+      </c>
+      <c r="I10" s="2">
+        <v>6.2</v>
       </c>
       <c r="J10">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1493,22 +1502,25 @@
         <v>31</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F11">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="G11" s="1">
-        <v>0</v>
+        <v>32.26</v>
       </c>
       <c r="H11" s="1">
-        <v>100</v>
+        <v>67.73999999999999</v>
+      </c>
+      <c r="I11" s="2">
+        <v>5.9</v>
       </c>
       <c r="J11">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1525,22 +1537,25 @@
         <v>34</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F12">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="G12" s="1">
-        <v>0</v>
+        <v>70.59</v>
       </c>
       <c r="H12" s="1">
-        <v>100</v>
+        <v>29.41</v>
+      </c>
+      <c r="I12" s="2">
+        <v>6.9</v>
       </c>
       <c r="J12">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -1557,22 +1572,25 @@
         <v>32</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F13">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="G13" s="1">
-        <v>0</v>
+        <v>15.63</v>
       </c>
       <c r="H13" s="1">
-        <v>100</v>
+        <v>84.38</v>
+      </c>
+      <c r="I13" s="2">
+        <v>5.1</v>
       </c>
       <c r="J13">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -1589,22 +1607,25 @@
         <v>24</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F14">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="G14" s="1">
-        <v>0</v>
+        <v>33.33</v>
       </c>
       <c r="H14" s="1">
-        <v>100</v>
+        <v>66.67</v>
+      </c>
+      <c r="I14" s="2">
+        <v>5</v>
       </c>
       <c r="J14">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K14" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -1621,22 +1642,25 @@
         <v>32</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F15">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="G15" s="1">
-        <v>0</v>
+        <v>28.13</v>
       </c>
       <c r="H15" s="1">
-        <v>100</v>
+        <v>71.88</v>
+      </c>
+      <c r="I15" s="2">
+        <v>5.1</v>
       </c>
       <c r="J15">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K15" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -2020,25 +2044,25 @@
         <v>36</v>
       </c>
       <c r="E8">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F8">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G8" s="1">
-        <v>83.33</v>
+        <v>91.67</v>
       </c>
       <c r="H8" s="1">
-        <v>16.67</v>
+        <v>8.33</v>
       </c>
       <c r="I8" s="2">
-        <v>8.300000000000001</v>
+        <v>8</v>
       </c>
       <c r="J8">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>16.67</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -2055,25 +2079,25 @@
         <v>36</v>
       </c>
       <c r="E9">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F9">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G9" s="1">
-        <v>69.44</v>
+        <v>77.78</v>
       </c>
       <c r="H9" s="1">
-        <v>30.56</v>
+        <v>22.22</v>
       </c>
       <c r="I9" s="2">
-        <v>7.8</v>
+        <v>7.1</v>
       </c>
       <c r="J9">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>30.56</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -2090,25 +2114,25 @@
         <v>33</v>
       </c>
       <c r="E10">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G10" s="1">
-        <v>69.7</v>
+        <v>72.73</v>
       </c>
       <c r="H10" s="1">
-        <v>30.3</v>
+        <v>27.27</v>
       </c>
       <c r="I10" s="2">
-        <v>7.6</v>
+        <v>6.7</v>
       </c>
       <c r="J10">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>30.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -2125,25 +2149,25 @@
         <v>31</v>
       </c>
       <c r="E11">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F11">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="G11" s="1">
-        <v>9.68</v>
+        <v>32.26</v>
       </c>
       <c r="H11" s="1">
-        <v>90.31999999999999</v>
+        <v>67.73999999999999</v>
       </c>
       <c r="I11" s="2">
-        <v>7.3</v>
+        <v>5.6</v>
       </c>
       <c r="J11">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>90.31999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -2160,25 +2184,25 @@
         <v>34</v>
       </c>
       <c r="E12">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F12">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G12" s="1">
-        <v>67.65000000000001</v>
+        <v>70.59</v>
       </c>
       <c r="H12" s="1">
-        <v>32.35</v>
+        <v>29.41</v>
       </c>
       <c r="I12" s="2">
-        <v>7.7</v>
+        <v>7</v>
       </c>
       <c r="J12">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>32.35</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -2195,19 +2219,19 @@
         <v>32</v>
       </c>
       <c r="E13">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="F13">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="G13" s="1">
-        <v>96.88</v>
+        <v>15.63</v>
       </c>
       <c r="H13" s="1">
-        <v>3.13</v>
+        <v>84.38</v>
       </c>
       <c r="I13" s="2">
-        <v>6.3</v>
+        <v>5.3</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -2230,19 +2254,19 @@
         <v>24</v>
       </c>
       <c r="E14">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="F14">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G14" s="1">
-        <v>83.33</v>
+        <v>33.33</v>
       </c>
       <c r="H14" s="1">
-        <v>16.67</v>
+        <v>66.67</v>
       </c>
       <c r="I14" s="2">
-        <v>6.3</v>
+        <v>5.5</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -2265,19 +2289,19 @@
         <v>32</v>
       </c>
       <c r="E15">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="F15">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="G15" s="1">
-        <v>93.75</v>
+        <v>28.13</v>
       </c>
       <c r="H15" s="1">
-        <v>6.25</v>
+        <v>71.88</v>
       </c>
       <c r="I15" s="2">
-        <v>6.4</v>
+        <v>5.5</v>
       </c>
       <c r="J15">
         <v>0</v>

--- a/academias/Física - Estadisticos 20212.xlsx
+++ b/academias/Física - Estadisticos 20212.xlsx
@@ -1362,25 +1362,25 @@
         <v>32</v>
       </c>
       <c r="E7">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F7">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G7" s="1">
-        <v>43.75</v>
+        <v>46.88</v>
       </c>
       <c r="H7" s="1">
-        <v>56.25</v>
+        <v>53.13</v>
       </c>
       <c r="I7" s="2">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="J7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K7" s="1">
-        <v>9.380000000000001</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="8" spans="1:11">

--- a/academias/Física - Estadisticos 20212.xlsx
+++ b/academias/Física - Estadisticos 20212.xlsx
@@ -1234,7 +1234,7 @@
         <v>70.83</v>
       </c>
       <c r="I3" s="2">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="J3">
         <v>4</v>
@@ -1572,19 +1572,19 @@
         <v>32</v>
       </c>
       <c r="E13">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="F13">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="G13" s="1">
-        <v>15.63</v>
+        <v>100</v>
       </c>
       <c r="H13" s="1">
-        <v>84.38</v>
+        <v>0</v>
       </c>
       <c r="I13" s="2">
-        <v>5.1</v>
+        <v>10</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -1607,19 +1607,19 @@
         <v>24</v>
       </c>
       <c r="E14">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="F14">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="G14" s="1">
-        <v>33.33</v>
+        <v>100</v>
       </c>
       <c r="H14" s="1">
-        <v>66.67</v>
+        <v>0</v>
       </c>
       <c r="I14" s="2">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -1642,19 +1642,19 @@
         <v>32</v>
       </c>
       <c r="E15">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="F15">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="G15" s="1">
-        <v>28.13</v>
+        <v>100</v>
       </c>
       <c r="H15" s="1">
-        <v>71.88</v>
+        <v>0</v>
       </c>
       <c r="I15" s="2">
-        <v>5.1</v>
+        <v>10</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -1881,7 +1881,7 @@
         <v>58.33</v>
       </c>
       <c r="I3" s="2">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -2044,19 +2044,19 @@
         <v>36</v>
       </c>
       <c r="E8">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G8" s="1">
-        <v>91.67</v>
+        <v>97.22</v>
       </c>
       <c r="H8" s="1">
-        <v>8.33</v>
+        <v>2.78</v>
       </c>
       <c r="I8" s="2">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -2079,19 +2079,19 @@
         <v>36</v>
       </c>
       <c r="E9">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="F9">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G9" s="1">
-        <v>77.78</v>
+        <v>91.67</v>
       </c>
       <c r="H9" s="1">
-        <v>22.22</v>
+        <v>8.33</v>
       </c>
       <c r="I9" s="2">
-        <v>7.1</v>
+        <v>7.5</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -2114,16 +2114,16 @@
         <v>33</v>
       </c>
       <c r="E10">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F10">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G10" s="1">
-        <v>72.73</v>
+        <v>84.84999999999999</v>
       </c>
       <c r="H10" s="1">
-        <v>27.27</v>
+        <v>15.15</v>
       </c>
       <c r="I10" s="2">
         <v>6.7</v>
@@ -2149,19 +2149,19 @@
         <v>31</v>
       </c>
       <c r="E11">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="F11">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="G11" s="1">
-        <v>32.26</v>
+        <v>80.65000000000001</v>
       </c>
       <c r="H11" s="1">
-        <v>67.73999999999999</v>
+        <v>19.35</v>
       </c>
       <c r="I11" s="2">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -2184,19 +2184,19 @@
         <v>34</v>
       </c>
       <c r="E12">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="F12">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G12" s="1">
-        <v>70.59</v>
+        <v>94.12</v>
       </c>
       <c r="H12" s="1">
-        <v>29.41</v>
+        <v>5.88</v>
       </c>
       <c r="I12" s="2">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -2219,19 +2219,19 @@
         <v>32</v>
       </c>
       <c r="E13">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="F13">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="G13" s="1">
-        <v>15.63</v>
+        <v>100</v>
       </c>
       <c r="H13" s="1">
-        <v>84.38</v>
+        <v>0</v>
       </c>
       <c r="I13" s="2">
-        <v>5.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -2254,19 +2254,19 @@
         <v>24</v>
       </c>
       <c r="E14">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="F14">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="G14" s="1">
-        <v>33.33</v>
+        <v>100</v>
       </c>
       <c r="H14" s="1">
-        <v>66.67</v>
+        <v>0</v>
       </c>
       <c r="I14" s="2">
-        <v>5.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -2289,19 +2289,19 @@
         <v>32</v>
       </c>
       <c r="E15">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="F15">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="G15" s="1">
-        <v>28.13</v>
+        <v>100</v>
       </c>
       <c r="H15" s="1">
-        <v>71.88</v>
+        <v>0</v>
       </c>
       <c r="I15" s="2">
-        <v>5.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J15">
         <v>0</v>

--- a/academias/Física - Estadisticos 20212.xlsx
+++ b/academias/Física - Estadisticos 20212.xlsx
@@ -1077,13 +1077,13 @@
         <v>65</v>
       </c>
       <c r="I17" s="2">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="J17">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K17" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -1100,25 +1100,25 @@
         <v>19</v>
       </c>
       <c r="E18">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F18">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G18" s="1">
-        <v>63.16</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="H18" s="1">
-        <v>36.84</v>
+        <v>26.32</v>
       </c>
       <c r="I18" s="2">
         <v>6.4</v>
       </c>
       <c r="J18">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K18" s="1">
-        <v>10.53</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1222,25 +1222,25 @@
         <v>24</v>
       </c>
       <c r="E3">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F3">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G3" s="1">
-        <v>29.17</v>
+        <v>41.67</v>
       </c>
       <c r="H3" s="1">
-        <v>70.83</v>
+        <v>58.33</v>
       </c>
       <c r="I3" s="2">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="J3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>16.67</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1327,25 +1327,25 @@
         <v>32</v>
       </c>
       <c r="E6">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F6">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G6" s="1">
-        <v>53.13</v>
+        <v>59.38</v>
       </c>
       <c r="H6" s="1">
-        <v>46.88</v>
+        <v>40.63</v>
       </c>
       <c r="I6" s="2">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="J6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>6.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1374,13 +1374,13 @@
         <v>53.13</v>
       </c>
       <c r="I7" s="2">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="J7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>6.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1677,25 +1677,25 @@
         <v>29</v>
       </c>
       <c r="E16">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F16">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G16" s="1">
-        <v>79.31</v>
+        <v>86.20999999999999</v>
       </c>
       <c r="H16" s="1">
-        <v>20.69</v>
+        <v>13.79</v>
       </c>
       <c r="I16" s="2">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="J16">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K16" s="1">
-        <v>10.34</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -1724,13 +1724,13 @@
         <v>65</v>
       </c>
       <c r="I17" s="2">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="J17">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K17" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -1747,25 +1747,25 @@
         <v>19</v>
       </c>
       <c r="E18">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F18">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G18" s="1">
-        <v>57.89</v>
+        <v>68.42</v>
       </c>
       <c r="H18" s="1">
-        <v>42.11</v>
+        <v>31.58</v>
       </c>
       <c r="I18" s="2">
         <v>7</v>
       </c>
       <c r="J18">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K18" s="1">
-        <v>10.53</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1834,19 +1834,19 @@
         <v>38</v>
       </c>
       <c r="E2">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="F2">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="G2" s="1">
-        <v>52.63</v>
+        <v>89.47</v>
       </c>
       <c r="H2" s="1">
-        <v>47.37</v>
+        <v>10.53</v>
       </c>
       <c r="I2" s="2">
-        <v>6.6</v>
+        <v>6.9</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -1869,19 +1869,19 @@
         <v>24</v>
       </c>
       <c r="E3">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="F3">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="G3" s="1">
-        <v>41.67</v>
+        <v>100</v>
       </c>
       <c r="H3" s="1">
-        <v>58.33</v>
+        <v>0</v>
       </c>
       <c r="I3" s="2">
-        <v>6</v>
+        <v>6.7</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -1904,19 +1904,19 @@
         <v>31</v>
       </c>
       <c r="E4">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="F4">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="G4" s="1">
-        <v>51.61</v>
+        <v>100</v>
       </c>
       <c r="H4" s="1">
-        <v>48.39</v>
+        <v>0</v>
       </c>
       <c r="I4" s="2">
-        <v>6.1</v>
+        <v>6.7</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -1939,19 +1939,19 @@
         <v>19</v>
       </c>
       <c r="E5">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F5">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G5" s="1">
-        <v>52.63</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="H5" s="1">
-        <v>47.37</v>
+        <v>15.79</v>
       </c>
       <c r="I5" s="2">
-        <v>6.2</v>
+        <v>6.7</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -1974,19 +1974,19 @@
         <v>32</v>
       </c>
       <c r="E6">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="F6">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G6" s="1">
-        <v>59.38</v>
+        <v>87.5</v>
       </c>
       <c r="H6" s="1">
-        <v>40.63</v>
+        <v>12.5</v>
       </c>
       <c r="I6" s="2">
-        <v>6.7</v>
+        <v>6.9</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -2009,19 +2009,19 @@
         <v>32</v>
       </c>
       <c r="E7">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="F7">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="G7" s="1">
-        <v>53.13</v>
+        <v>90.63</v>
       </c>
       <c r="H7" s="1">
-        <v>46.88</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="I7" s="2">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="I13" s="2">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -2266,7 +2266,7 @@
         <v>0</v>
       </c>
       <c r="I14" s="2">
-        <v>8.300000000000001</v>
+        <v>8</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -2301,7 +2301,7 @@
         <v>0</v>
       </c>
       <c r="I15" s="2">
-        <v>8.300000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -2324,16 +2324,16 @@
         <v>29</v>
       </c>
       <c r="E16">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F16">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G16" s="1">
-        <v>86.20999999999999</v>
+        <v>82.76000000000001</v>
       </c>
       <c r="H16" s="1">
-        <v>13.79</v>
+        <v>17.24</v>
       </c>
       <c r="I16" s="2">
         <v>6.8</v>
@@ -2359,25 +2359,25 @@
         <v>20</v>
       </c>
       <c r="E17">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F17">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G17" s="1">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="H17" s="1">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="I17" s="2">
-        <v>5.8</v>
+        <v>6.1</v>
       </c>
       <c r="J17">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K17" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -2394,25 +2394,25 @@
         <v>19</v>
       </c>
       <c r="E18">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F18">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G18" s="1">
-        <v>57.89</v>
+        <v>78.95</v>
       </c>
       <c r="H18" s="1">
-        <v>42.11</v>
+        <v>21.05</v>
       </c>
       <c r="I18" s="2">
-        <v>6.9</v>
+        <v>6.7</v>
       </c>
       <c r="J18">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K18" s="1">
-        <v>10.53</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
